--- a/工作-大圣牌/战棋/阵营流派教学关卡.xlsx
+++ b/工作-大圣牌/战棋/阵营流派教学关卡.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Documents\GitHub\Notes\工作-大圣牌\战棋\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\Obsidian Vault\工作-大圣牌\战棋\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D35E4B67-F0CC-487C-A800-6A5469989A41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A097EFDF-2AF9-4038-98BB-A2670EF77339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{6251870B-EF66-476A-BC24-438CA65D56C0}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6251870B-EF66-476A-BC24-438CA65D56C0}"/>
   </bookViews>
   <sheets>
     <sheet name="阵营流派教学" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>友方登场部将</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -141,6 +141,26 @@
   </si>
   <si>
     <t>美猴王，马流元帅，大猿神</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美猴王，</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天庭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>狮驼岭</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙宫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>地府</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -212,9 +232,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 主题">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -252,7 +272,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -358,7 +378,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,7 +520,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -508,24 +528,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8404D20-B456-4106-BC03-A21D19FEFD61}">
-  <dimension ref="A1:O9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="8.6640625"/>
     <col min="4" max="4" width="12.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13.58203125" style="1" customWidth="1"/>
     <col min="6" max="7" width="21.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="41.125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="41.08203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="39.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="21.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="21.625" customWidth="1"/>
-    <col min="13" max="13" width="18.625" style="1" customWidth="1"/>
-    <col min="14" max="14" width="12.875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="13.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="21.08203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="21.58203125" customWidth="1"/>
+    <col min="12" max="12" width="8.6640625"/>
+    <col min="13" max="13" width="18.58203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="12.83203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" style="1" customWidth="1"/>
     <col min="16" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
@@ -572,7 +594,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" ht="84" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
@@ -594,7 +616,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="85.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:15" ht="84" x14ac:dyDescent="0.3">
       <c r="C3" s="1"/>
       <c r="D3" s="1">
         <v>1</v>
@@ -614,21 +636,21 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>2</v>
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <v>3</v>
       </c>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:15" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" ht="28" x14ac:dyDescent="0.3">
       <c r="C6" s="1"/>
       <c r="E6" s="1" t="s">
         <v>9</v>
@@ -637,10 +659,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
       <c r="E9" s="1" t="s">
         <v>10</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.3">
+      <c r="B28" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
